--- a/data paper.xlsx
+++ b/data paper.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://olvp-my.sharepoint.com/personal/lukas_vlaeminck_vlot_be/Documents/school jaar 2025-2026/Einde project/Experiment/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2000" documentId="8_{848A0AF6-95E5-4E6D-810F-315D5A952DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A682C03-0861-41AC-A487-6E2F6B7BFCF8}"/>
+  <xr:revisionPtr revIDLastSave="2016" documentId="8_{848A0AF6-95E5-4E6D-810F-315D5A952DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A4DBF8-F06C-41DA-A94B-303353DF65E7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="1000" activeTab="6" xr2:uid="{A2FB32E4-44EB-42A2-848A-7FE4FE0D1500}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13740" tabRatio="1000" activeTab="3" xr2:uid="{A2FB32E4-44EB-42A2-848A-7FE4FE0D1500}"/>
   </bookViews>
   <sheets>
     <sheet name="ARP-replys detection method" sheetId="1" r:id="rId1"/>
@@ -233,9 +233,6 @@
     <t>min</t>
   </si>
   <si>
-    <t>normalisation</t>
-  </si>
-  <si>
     <t>Feasibility of MITM Attacks</t>
   </si>
   <si>
@@ -252,6 +249,9 @@
   </si>
   <si>
     <t>False Positives</t>
+  </si>
+  <si>
+    <t>invers normalisation</t>
   </si>
 </sst>
 </file>
@@ -898,7 +898,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="nl-BE"/>
+              <a:rPr lang="nl-BE" sz="1600" b="1"/>
               <a:t>Speed</a:t>
             </a:r>
           </a:p>
@@ -956,7 +956,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent3"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1074,7 +1074,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1561,7 +1561,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1660,7 +1660,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2055,7 +2055,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>normalisation</c:v>
+                  <c:v>invers normalisation</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2074,7 +2074,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0" formatCode="0%">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2179,7 +2179,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>normalisation</c:v>
+                  <c:v>invers normalisation</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2198,7 +2198,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0" formatCode="0%">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2303,7 +2303,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>normalisation</c:v>
+                  <c:v>invers normalisation</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2322,7 +2322,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0" formatCode="0%">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2562,7 +2562,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent3"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2810,7 +2810,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -6996,6 +6996,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
   <a:themeElements>
@@ -13400,10 +13404,10 @@
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>40</v>
@@ -13432,7 +13436,7 @@
         <v>39</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I6" s="3">
         <f>F7*$B$3+G14*$C$3+G21*$D$3</f>
@@ -13445,7 +13449,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3">
         <f>MAX('ARP-replys detection method'!B24:F24)</f>
@@ -13547,7 +13551,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>53</v>
@@ -13562,7 +13566,7 @@
         <v>51</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>39</v>
@@ -13570,7 +13574,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="3">
         <f>MAX('ARP-replys detection method'!B50:F50)</f>
@@ -13589,8 +13593,8 @@
         <v>100</v>
       </c>
       <c r="F14" s="49">
-        <f>G14</f>
-        <v>1</v>
+        <f>1-G14</f>
+        <v>0</v>
       </c>
       <c r="G14" s="20">
         <f>IF((effectiviteit!B14-effectiviteit!C14)=0,1,('ARP-replys detection method'!G50-C14)/(B14-C14))</f>
@@ -13618,8 +13622,8 @@
         <v>100</v>
       </c>
       <c r="F15" s="50">
-        <f>G15</f>
-        <v>1</v>
+        <f>1-G15</f>
+        <v>0</v>
       </c>
       <c r="G15" s="11">
         <f>IF((effectiviteit!B15-effectiviteit!C15)=0,1,('ARP-replys detection method'!G51-C15)/(B15-C15))</f>
@@ -13647,8 +13651,8 @@
         <v>100</v>
       </c>
       <c r="F16" s="51">
-        <f>G16</f>
-        <v>1</v>
+        <f>1-G16</f>
+        <v>0</v>
       </c>
       <c r="G16" s="14">
         <f>IF((effectiviteit!B16-effectiviteit!C16)=0,1,('ARP-replys detection method'!G52-C16)/(B16-C16))</f>
@@ -13662,7 +13666,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>54</v>
@@ -13685,7 +13689,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B21" s="3">
         <f>MAX('ARP-replys detection method'!J24:N24)</f>
@@ -13725,11 +13729,11 @@
         <v>0.75</v>
       </c>
       <c r="D22">
-        <f t="shared" ref="D22:E23" si="3">B22*100</f>
+        <f>B22*100</f>
         <v>100</v>
       </c>
       <c r="E22">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D22:E23" si="3">C22*100</f>
         <v>75</v>
       </c>
       <c r="F22" s="50">
@@ -23445,7 +23449,7 @@
         <v>44</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>45</v>
